--- a/Excel/PetSkinConfig.xlsx
+++ b/Excel/PetSkinConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B507B8-82EA-4302-8D30-3F16F31347E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6323DA5F-927D-4094-930F-99CC46E9BB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="99">
   <si>
     <t>Id</t>
   </si>
@@ -227,6 +227,140 @@
   </si>
   <si>
     <t>变异:光明天使</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name_EN</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>PripertyShow_EN</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dazed</t>
+  </si>
+  <si>
+    <t>Mutation: Stunned</t>
+  </si>
+  <si>
+    <t>Snooze</t>
+  </si>
+  <si>
+    <t>Variant: Loose</t>
+  </si>
+  <si>
+    <t>Gray Gray</t>
+  </si>
+  <si>
+    <t>Variant: Grey</t>
+  </si>
+  <si>
+    <t>Small palm</t>
+  </si>
+  <si>
+    <t>Mutation: Small Palm</t>
+  </si>
+  <si>
+    <t>Xiaohong</t>
+  </si>
+  <si>
+    <t>Mutation: Little Red</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>Mutation: Little Blue</t>
+  </si>
+  <si>
+    <t>Little Green</t>
+  </si>
+  <si>
+    <t>Variant: Small Green</t>
+  </si>
+  <si>
+    <t>BoBo</t>
+  </si>
+  <si>
+    <t>Mutation: Pibo</t>
+  </si>
+  <si>
+    <t>Thunder Pig</t>
+  </si>
+  <si>
+    <t>Mutation: Thunder Pig</t>
+  </si>
+  <si>
+    <t>Octopus Lady</t>
+  </si>
+  <si>
+    <t>Variant: Squid Lady</t>
+  </si>
+  <si>
+    <t>Magic Elves</t>
+  </si>
+  <si>
+    <t>Mutation: Magic Spirit</t>
+  </si>
+  <si>
+    <t>Magic Doll</t>
+  </si>
+  <si>
+    <t>Mutation: Magic Doll</t>
+  </si>
+  <si>
+    <t>Naughty Dingding</t>
+  </si>
+  <si>
+    <t>Mutation: Naughty Dingding</t>
+  </si>
+  <si>
+    <t>Light Angel</t>
+  </si>
+  <si>
+    <t>Mutation: Light Angel</t>
+  </si>
+  <si>
+    <t>Ironclad Warrior</t>
+  </si>
+  <si>
+    <t>Mutation: Ironclad Warrior</t>
+  </si>
+  <si>
+    <t>Spirit Fox Demon</t>
+  </si>
+  <si>
+    <t>Mutation: Spirit Fox Demon</t>
+  </si>
+  <si>
+    <t>Loving Spirit</t>
+  </si>
+  <si>
+    <t>Variant: Spirit of Love</t>
+  </si>
+  <si>
+    <t>Legendary Beast: Elf Deer</t>
+  </si>
+  <si>
+    <t>Legendary Beast: Yuguang Qingqing</t>
+  </si>
+  <si>
+    <t>Legendary Beast: Divine Dragon of the Immortal Realm</t>
+  </si>
+  <si>
+    <t>All stats increased by 5%</t>
+  </si>
+  <si>
+    <t>All stats increased by 3%</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>All stats increased by 10%</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1393,7 +1527,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1412,6 +1546,7 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="314">
     <cellStyle name="20% - 强调文字颜色 1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -2055,18 +2190,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:H66"/>
+  <dimension ref="B1:J66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.5" customWidth="1"/>
     <col min="3" max="3" width="18.875" customWidth="1"/>
-    <col min="4" max="6" width="17.875" customWidth="1"/>
-    <col min="7" max="7" width="57.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.875" customWidth="1"/>
+    <col min="4" max="7" width="17.875" customWidth="1"/>
+    <col min="8" max="8" width="57.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.875" customWidth="1"/>
+    <col min="10" max="10" width="24.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:10" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="E2" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2074,19 +2218,25 @@
         <v>1</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -2094,19 +2244,25 @@
         <v>6</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J4" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2114,19 +2270,25 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="5"/>
       <c r="C6" s="6">
         <v>10101</v>
@@ -2134,18 +2296,22 @@
       <c r="D6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="6">
-        <v>1000101</v>
+      <c r="E6" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="F6" s="6">
         <v>1000101</v>
       </c>
       <c r="G6" s="6">
+        <v>1000101</v>
+      </c>
+      <c r="H6" s="6">
         <v>0</v>
       </c>
-      <c r="H6" s="6"/>
-    </row>
-    <row r="7" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="5"/>
       <c r="C7" s="6">
         <v>10102</v>
@@ -2153,1125 +2319,1441 @@
       <c r="D7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="6">
-        <v>1000102</v>
+      <c r="E7" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="F7" s="6">
         <v>1000102</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="6">
+        <v>1000102</v>
+      </c>
+      <c r="H7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="I7" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J7" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="6">
         <v>20101</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="6">
-        <v>1000201</v>
+      <c r="E8" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="F8" s="6">
         <v>1000201</v>
       </c>
       <c r="G8" s="6">
+        <v>1000201</v>
+      </c>
+      <c r="H8" s="6">
         <v>0</v>
       </c>
-      <c r="H8" s="6"/>
-    </row>
-    <row r="9" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="6">
         <v>20102</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="6">
-        <v>1000202</v>
+      <c r="E9" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="F9" s="6">
         <v>1000202</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="6">
+        <v>1000202</v>
+      </c>
+      <c r="H9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="I9" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J9" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="6">
         <v>30101</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="6">
-        <v>1000301</v>
+      <c r="E10" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="F10" s="6">
         <v>1000301</v>
       </c>
       <c r="G10" s="6">
+        <v>1000301</v>
+      </c>
+      <c r="H10" s="6">
         <v>0</v>
       </c>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+    </row>
+    <row r="11" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11" s="6">
         <v>30102</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="6">
-        <v>1000302</v>
+      <c r="E11" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="F11" s="6">
         <v>1000302</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="6">
+        <v>1000302</v>
+      </c>
+      <c r="H11" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="I11" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J11" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="6">
         <v>40101</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="6">
-        <v>1000401</v>
+      <c r="E12" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="F12" s="6">
         <v>1000401</v>
       </c>
       <c r="G12" s="6">
+        <v>1000401</v>
+      </c>
+      <c r="H12" s="6">
         <v>0</v>
       </c>
-      <c r="H12" s="6"/>
-    </row>
-    <row r="13" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+    </row>
+    <row r="13" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C13" s="6">
         <v>40102</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="6">
-        <v>1000402</v>
+      <c r="E13" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="F13" s="6">
         <v>1000402</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="6">
+        <v>1000402</v>
+      </c>
+      <c r="H13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="I13" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J13" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C14" s="6">
         <v>401031</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="6">
-        <v>1000403</v>
+      <c r="E14" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="F14" s="6">
         <v>1000403</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="6">
+        <v>1000403</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="I14" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J14" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="6">
         <v>401042</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="6">
-        <v>1000404</v>
+      <c r="E15" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="F15" s="6">
         <v>1000404</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="6">
+        <v>1000404</v>
+      </c>
+      <c r="H15" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="I15" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="16" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J15" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C16" s="6">
         <v>50101</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="6">
-        <v>1000501</v>
+      <c r="E16" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="F16" s="6">
         <v>1000501</v>
       </c>
       <c r="G16" s="6">
+        <v>1000501</v>
+      </c>
+      <c r="H16" s="6">
         <v>0</v>
       </c>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+    </row>
+    <row r="17" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="6">
         <v>50102</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="6">
-        <v>1000502</v>
+      <c r="E17" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="F17" s="6">
         <v>1000502</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="6">
+        <v>1000502</v>
+      </c>
+      <c r="H17" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="I17" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="18" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J17" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="6">
         <v>501031</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="6">
-        <v>1000503</v>
+      <c r="E18" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="F18" s="6">
         <v>1000503</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="6">
+        <v>1000503</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="I18" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J18" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C19" s="6">
         <v>501041</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="6">
-        <v>1000504</v>
+      <c r="E19" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="F19" s="6">
         <v>1000504</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="6">
+        <v>1000504</v>
+      </c>
+      <c r="H19" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="I19" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J19" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C20" s="6">
         <v>60101</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="6">
-        <v>1000601</v>
+      <c r="E20" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="F20" s="6">
         <v>1000601</v>
       </c>
       <c r="G20" s="6">
+        <v>1000601</v>
+      </c>
+      <c r="H20" s="6">
         <v>0</v>
       </c>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+    </row>
+    <row r="21" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C21" s="6">
         <v>60102</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E21" s="6">
-        <v>1000602</v>
+      <c r="E21" s="6" t="s">
+        <v>69</v>
       </c>
       <c r="F21" s="6">
         <v>1000602</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="6">
+        <v>1000602</v>
+      </c>
+      <c r="H21" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="I21" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="22" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J21" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C22" s="6">
         <v>601031</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E22" s="6">
-        <v>1000603</v>
+      <c r="E22" s="6" t="s">
+        <v>69</v>
       </c>
       <c r="F22" s="6">
         <v>1000603</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="6">
+        <v>1000603</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="I22" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J22" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C23" s="6">
         <v>70101</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="6">
-        <v>1000701</v>
+      <c r="E23" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="F23" s="6">
         <v>1000701</v>
       </c>
       <c r="G23" s="6">
+        <v>1000701</v>
+      </c>
+      <c r="H23" s="6">
         <v>0</v>
       </c>
-      <c r="H23" s="6"/>
-    </row>
-    <row r="24" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+    </row>
+    <row r="24" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C24" s="6">
         <v>70102</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="6">
-        <v>1000702</v>
+      <c r="E24" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="F24" s="6">
         <v>1000702</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="6">
+        <v>1000702</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="I24" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="25" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J24" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C25" s="6">
         <v>701031</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E25" s="6">
-        <v>1000703</v>
+      <c r="E25" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="F25" s="6">
         <v>1000703</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="6">
+        <v>1000703</v>
+      </c>
+      <c r="H25" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="I25" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="26" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J25" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C26" s="6">
         <v>701041</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E26" s="6">
-        <v>1000704</v>
+      <c r="E26" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="F26" s="6">
         <v>1000704</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="6">
+        <v>1000704</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="I26" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="27" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J26" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C27" s="6">
         <v>80101</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="6">
-        <v>1000801</v>
+      <c r="E27" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="F27" s="6">
         <v>1000801</v>
       </c>
       <c r="G27" s="6">
+        <v>1000801</v>
+      </c>
+      <c r="H27" s="6">
         <v>0</v>
       </c>
-      <c r="H27" s="6"/>
-    </row>
-    <row r="28" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+    </row>
+    <row r="28" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C28" s="6">
         <v>80102</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E28" s="6">
-        <v>1000802</v>
+      <c r="E28" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="F28" s="6">
         <v>1000802</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="6">
+        <v>1000802</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="I28" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="29" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J28" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C29" s="6">
         <v>90101</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E29" s="6">
-        <v>1000901</v>
+      <c r="E29" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="F29" s="6">
         <v>1000901</v>
       </c>
       <c r="G29" s="6">
+        <v>1000901</v>
+      </c>
+      <c r="H29" s="6">
         <v>0</v>
       </c>
-      <c r="H29" s="6"/>
-    </row>
-    <row r="30" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+    </row>
+    <row r="30" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C30" s="6">
         <v>90102</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E30" s="6">
-        <v>1000902</v>
+      <c r="E30" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="F30" s="6">
         <v>1000902</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="6">
+        <v>1000902</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="I30" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="31" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J30" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C31" s="6">
         <v>901031</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="6">
-        <v>1000903</v>
+      <c r="E31" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="F31" s="6">
         <v>1000903</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G31" s="6">
+        <v>1000903</v>
+      </c>
+      <c r="H31" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H31" s="6" t="s">
+      <c r="I31" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="32" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J31" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C32" s="6">
         <v>901041</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="6">
-        <v>1000904</v>
+      <c r="E32" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="F32" s="6">
         <v>1000904</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" s="6">
+        <v>1000904</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H32" s="6" t="s">
+      <c r="I32" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="33" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J32" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C33" s="6">
         <v>100101</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E33" s="6">
-        <v>1001001</v>
+      <c r="E33" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="F33" s="6">
         <v>1001001</v>
       </c>
       <c r="G33" s="6">
+        <v>1001001</v>
+      </c>
+      <c r="H33" s="6">
         <v>0</v>
       </c>
-      <c r="H33" s="6"/>
-    </row>
-    <row r="34" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+    </row>
+    <row r="34" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C34" s="6">
         <v>100102</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E34" s="6">
-        <v>1001002</v>
+      <c r="E34" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="F34" s="6">
         <v>1001002</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" s="6">
+        <v>1001002</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H34" s="6" t="s">
+      <c r="I34" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="35" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J34" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C35" s="6">
         <v>1001031</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E35" s="6">
-        <v>1001003</v>
+      <c r="E35" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="F35" s="6">
         <v>1001003</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" s="6">
+        <v>1001003</v>
+      </c>
+      <c r="H35" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H35" s="6" t="s">
+      <c r="I35" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="36" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J35" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C36" s="6">
         <v>1001041</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E36" s="6">
-        <v>1001004</v>
+      <c r="E36" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="F36" s="6">
         <v>1001004</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="G36" s="6">
+        <v>1001004</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H36" s="6" t="s">
+      <c r="I36" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="37" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J36" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C37" s="6">
         <v>110101</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E37" s="6">
-        <v>1001101</v>
+      <c r="E37" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="F37" s="6">
         <v>1001101</v>
       </c>
       <c r="G37" s="6">
+        <v>1001101</v>
+      </c>
+      <c r="H37" s="6">
         <v>0</v>
       </c>
-      <c r="H37" s="6"/>
-    </row>
-    <row r="38" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+    </row>
+    <row r="38" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C38" s="6">
         <v>110102</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E38" s="6">
-        <v>1001102</v>
+      <c r="E38" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="F38" s="6">
         <v>1001102</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="G38" s="6">
+        <v>1001102</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H38" s="6" t="s">
+      <c r="I38" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="39" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J38" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C39" s="6">
         <v>1101031</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E39" s="6">
-        <v>1001103</v>
+      <c r="E39" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="F39" s="6">
         <v>1001103</v>
       </c>
-      <c r="G39" s="6" t="s">
+      <c r="G39" s="6">
+        <v>1001103</v>
+      </c>
+      <c r="H39" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H39" s="6" t="s">
+      <c r="I39" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="40" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J39" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="40" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C40" s="6">
         <v>120101</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E40" s="6">
-        <v>1001201</v>
+      <c r="E40" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="F40" s="6">
         <v>1001201</v>
       </c>
       <c r="G40" s="6">
+        <v>1001201</v>
+      </c>
+      <c r="H40" s="6">
         <v>0</v>
       </c>
-      <c r="H40" s="6"/>
-    </row>
-    <row r="41" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+    </row>
+    <row r="41" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C41" s="6">
         <v>120102</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E41" s="6">
-        <v>1001202</v>
+      <c r="E41" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="F41" s="6">
         <v>1001202</v>
       </c>
-      <c r="G41" s="6" t="s">
+      <c r="G41" s="6">
+        <v>1001202</v>
+      </c>
+      <c r="H41" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H41" s="6" t="s">
+      <c r="I41" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="42" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J41" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C42" s="6">
         <v>1201031</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E42" s="6">
-        <v>1001203</v>
+      <c r="E42" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="F42" s="6">
         <v>1001203</v>
       </c>
-      <c r="G42" s="6" t="s">
+      <c r="G42" s="6">
+        <v>1001203</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H42" s="6" t="s">
+      <c r="I42" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="43" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J42" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="43" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C43" s="6">
         <v>130101</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E43" s="6">
-        <v>1001301</v>
+      <c r="E43" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="F43" s="6">
         <v>1001301</v>
       </c>
       <c r="G43" s="6">
+        <v>1001301</v>
+      </c>
+      <c r="H43" s="6">
         <v>0</v>
       </c>
-      <c r="H43" s="6"/>
-    </row>
-    <row r="44" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+    </row>
+    <row r="44" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C44" s="6">
         <v>130102</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E44" s="6">
-        <v>1001302</v>
+      <c r="E44" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="F44" s="6">
         <v>1001302</v>
       </c>
-      <c r="G44" s="6" t="s">
+      <c r="G44" s="6">
+        <v>1001302</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H44" s="6" t="s">
+      <c r="I44" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="45" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J44" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C45" s="6">
         <v>1301031</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E45" s="6">
-        <v>1001303</v>
+      <c r="E45" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="F45" s="6">
         <v>1001303</v>
       </c>
-      <c r="G45" s="6" t="s">
+      <c r="G45" s="6">
+        <v>1001303</v>
+      </c>
+      <c r="H45" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H45" s="6" t="s">
+      <c r="I45" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J45" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="46" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C46" s="6">
         <v>1301041</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E46" s="6">
-        <v>1001304</v>
+      <c r="E46" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="F46" s="6">
         <v>1001304</v>
       </c>
-      <c r="G46" s="6" t="s">
+      <c r="G46" s="6">
+        <v>1001304</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H46" s="6" t="s">
+      <c r="I46" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="47" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J46" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="47" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C47" s="6">
         <v>140101</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E47" s="6">
-        <v>1001401</v>
+      <c r="E47" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="F47" s="6">
         <v>1001401</v>
       </c>
       <c r="G47" s="6">
+        <v>1001401</v>
+      </c>
+      <c r="H47" s="6">
         <v>0</v>
       </c>
-      <c r="H47" s="6"/>
-    </row>
-    <row r="48" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+    </row>
+    <row r="48" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C48" s="6">
         <v>140102</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E48" s="6">
-        <v>1001402</v>
+      <c r="E48" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="F48" s="6">
         <v>1001402</v>
       </c>
-      <c r="G48" s="6" t="s">
+      <c r="G48" s="6">
+        <v>1001402</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H48" s="6" t="s">
+      <c r="I48" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="49" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J48" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C49" s="6">
         <v>1401031</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="6">
-        <v>1001403</v>
+      <c r="E49" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="F49" s="6">
         <v>1001403</v>
       </c>
-      <c r="G49" s="6" t="s">
+      <c r="G49" s="6">
+        <v>1001403</v>
+      </c>
+      <c r="H49" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H49" s="6" t="s">
+      <c r="I49" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="50" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J49" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C50" s="6">
         <v>910101</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E50" s="6">
-        <v>1009101</v>
+      <c r="E50" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="F50" s="6">
         <v>1009101</v>
       </c>
       <c r="G50" s="6">
+        <v>1009101</v>
+      </c>
+      <c r="H50" s="6">
         <v>0</v>
       </c>
-      <c r="H50" s="6"/>
-    </row>
-    <row r="51" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+    </row>
+    <row r="51" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C51" s="6">
         <v>910102</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E51" s="6">
-        <v>1009102</v>
+      <c r="E51" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="F51" s="6">
         <v>1009102</v>
       </c>
-      <c r="G51" s="6" t="s">
+      <c r="G51" s="6">
+        <v>1009102</v>
+      </c>
+      <c r="H51" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H51" s="6" t="s">
+      <c r="I51" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="52" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J51" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="52" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C52" s="6">
         <v>9101031</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E52" s="6">
-        <v>1009103</v>
+      <c r="E52" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="F52" s="6">
         <v>1009103</v>
       </c>
-      <c r="G52" s="6" t="s">
+      <c r="G52" s="6">
+        <v>1009103</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H52" s="6" t="s">
+      <c r="I52" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J52" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="53" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C53" s="6">
         <v>9101041</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E53" s="6">
-        <v>1009104</v>
+      <c r="E53" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="F53" s="6">
         <v>1009104</v>
       </c>
-      <c r="G53" s="6" t="s">
+      <c r="G53" s="6">
+        <v>1009104</v>
+      </c>
+      <c r="H53" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H53" s="6" t="s">
+      <c r="I53" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="54" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J53" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="54" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C54" s="6">
         <v>920101</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E54" s="6">
-        <v>1009201</v>
+      <c r="E54" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="F54" s="6">
         <v>1009201</v>
       </c>
       <c r="G54" s="6">
+        <v>1009201</v>
+      </c>
+      <c r="H54" s="6">
         <v>0</v>
       </c>
-      <c r="H54" s="6"/>
-    </row>
-    <row r="55" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+    </row>
+    <row r="55" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C55" s="6">
         <v>920102</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E55" s="6">
-        <v>1009202</v>
+      <c r="E55" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="F55" s="6">
         <v>1009202</v>
       </c>
-      <c r="G55" s="6" t="s">
+      <c r="G55" s="6">
+        <v>1009202</v>
+      </c>
+      <c r="H55" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H55" s="6" t="s">
+      <c r="I55" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="56" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J55" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="56" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C56" s="6">
         <v>9201031</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E56" s="6">
-        <v>1009203</v>
+      <c r="E56" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="F56" s="6">
         <v>1009203</v>
       </c>
-      <c r="G56" s="6" t="s">
+      <c r="G56" s="6">
+        <v>1009203</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H56" s="6" t="s">
+      <c r="I56" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="57" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J56" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="57" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C57" s="6">
         <v>9201041</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E57" s="6">
-        <v>1009204</v>
+      <c r="E57" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="F57" s="6">
         <v>1009204</v>
       </c>
-      <c r="G57" s="6" t="s">
+      <c r="G57" s="6">
+        <v>1009204</v>
+      </c>
+      <c r="H57" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H57" s="6" t="s">
+      <c r="I57" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="58" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J57" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="58" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C58" s="6">
         <v>930101</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E58" s="6">
-        <v>1009301</v>
+      <c r="E58" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="F58" s="6">
         <v>1009301</v>
       </c>
       <c r="G58" s="6">
+        <v>1009301</v>
+      </c>
+      <c r="H58" s="6">
         <v>0</v>
       </c>
-      <c r="H58" s="6"/>
-    </row>
-    <row r="59" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+    </row>
+    <row r="59" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C59" s="6">
         <v>930102</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E59" s="6">
-        <v>1009302</v>
+      <c r="E59" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="F59" s="6">
         <v>1009302</v>
       </c>
-      <c r="G59" s="6" t="s">
+      <c r="G59" s="6">
+        <v>1009302</v>
+      </c>
+      <c r="H59" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H59" s="6" t="s">
+      <c r="I59" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="60" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J59" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="60" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C60" s="6">
         <v>9301031</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E60" s="6">
-        <v>1009303</v>
+      <c r="E60" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="F60" s="6">
         <v>1009303</v>
       </c>
-      <c r="G60" s="6" t="s">
+      <c r="G60" s="6">
+        <v>1009303</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H60" s="6" t="s">
+      <c r="I60" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J60" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="61" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C61" s="6">
         <v>9301041</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E61" s="6">
-        <v>1009304</v>
+      <c r="E61" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="F61" s="6">
         <v>1009304</v>
       </c>
-      <c r="G61" s="6" t="s">
+      <c r="G61" s="6">
+        <v>1009304</v>
+      </c>
+      <c r="H61" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H61" s="6" t="s">
+      <c r="I61" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="62" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J61" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="62" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C62" s="6">
         <v>200001</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E62" s="6">
-        <v>2000001</v>
+      <c r="E62" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="F62" s="6">
         <v>2000001</v>
       </c>
-      <c r="G62" s="6" t="s">
+      <c r="G62" s="6">
+        <v>2000001</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H62" s="6" t="s">
+      <c r="I62" s="6" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="63" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J62" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="63" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C63" s="6">
         <v>200002</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E63" s="6">
-        <v>2000002</v>
+      <c r="E63" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="F63" s="6">
         <v>2000002</v>
       </c>
-      <c r="G63" s="6" t="s">
+      <c r="G63" s="6">
+        <v>2000002</v>
+      </c>
+      <c r="H63" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H63" s="6" t="s">
+      <c r="I63" s="6" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="64" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J63" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="64" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C64" s="6">
         <v>200003</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E64" s="6">
-        <v>2000003</v>
+      <c r="E64" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="F64" s="6">
         <v>2000003</v>
       </c>
-      <c r="G64" s="6" t="s">
+      <c r="G64" s="6">
+        <v>2000003</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H64" s="6" t="s">
+      <c r="I64" s="6" t="s">
         <v>19</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
